--- a/12609979.2.xlsx
+++ b/12609979.2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DA04AD-772C-44AC-AAEC-BA959347ED94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{5ACB5D22-18EE-4E8C-AA38-09B6EED47307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3B63BDC-8D68-440C-A009-D6E2B4F10D9D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>project work</t>
+  </si>
+  <si>
+    <t>learning how to use git and working on project</t>
   </si>
 </sst>
 </file>
@@ -2994,27 +2997,51 @@
         <v>103</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10" t="str">
+    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B47" s="9">
+        <v>400</v>
+      </c>
+      <c r="C47" s="9">
+        <v>60</v>
+      </c>
+      <c r="D47" s="9">
+        <v>180</v>
+      </c>
+      <c r="E47" s="9">
+        <v>60</v>
+      </c>
+      <c r="F47" s="9">
+        <v>300</v>
+      </c>
+      <c r="G47" s="9">
+        <v>6</v>
+      </c>
+      <c r="H47" s="9">
+        <v>400</v>
+      </c>
+      <c r="I47" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J47" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>

--- a/12609979.2.xlsx
+++ b/12609979.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{5ACB5D22-18EE-4E8C-AA38-09B6EED47307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3B63BDC-8D68-440C-A009-D6E2B4F10D9D}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{5ACB5D22-18EE-4E8C-AA38-09B6EED47307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81771F08-CCC3-480B-A1A0-A8418AEE2D24}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3043,27 +3043,51 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10" t="str">
+    <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B48" s="9">
+        <v>450</v>
+      </c>
+      <c r="C48" s="9">
+        <v>60</v>
+      </c>
+      <c r="D48" s="9">
+        <v>120</v>
+      </c>
+      <c r="E48" s="9">
+        <v>120</v>
+      </c>
+      <c r="F48" s="9">
+        <v>300</v>
+      </c>
+      <c r="G48" s="9">
+        <v>6</v>
+      </c>
+      <c r="H48" s="9">
+        <v>360</v>
+      </c>
+      <c r="I48" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J48" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="12"/>
+        <v>30</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>

--- a/12609979.2.xlsx
+++ b/12609979.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{5ACB5D22-18EE-4E8C-AA38-09B6EED47307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81771F08-CCC3-480B-A1A0-A8418AEE2D24}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{5ACB5D22-18EE-4E8C-AA38-09B6EED47307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC15D42C-F061-404B-8094-71E224527C9B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3090,26 +3090,50 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="10" t="str">
+      <c r="A49" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B49" s="9">
+        <v>450</v>
+      </c>
+      <c r="C49" s="9">
+        <v>70</v>
+      </c>
+      <c r="D49" s="9">
+        <v>120</v>
+      </c>
+      <c r="E49" s="9">
+        <v>80</v>
+      </c>
+      <c r="F49" s="9">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9">
+        <v>480</v>
+      </c>
+      <c r="I49" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="10" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J49" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="12"/>
+        <v>240</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="12" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>

--- a/12609979.2.xlsx
+++ b/12609979.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{5ACB5D22-18EE-4E8C-AA38-09B6EED47307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC15D42C-F061-404B-8094-71E224527C9B}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{5ACB5D22-18EE-4E8C-AA38-09B6EED47307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{691D1AA9-2311-49A0-B3D3-7AC8D634A2CE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>learning how to use git and working on project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stressful day </t>
   </si>
 </sst>
 </file>
@@ -3136,26 +3139,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="10" t="str">
+      <c r="A50" s="8">
+        <v>46292</v>
+      </c>
+      <c r="B50" s="9">
+        <v>300</v>
+      </c>
+      <c r="C50" s="9">
+        <v>70</v>
+      </c>
+      <c r="D50" s="9">
+        <v>120</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>480</v>
+      </c>
+      <c r="I50" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="10" t="str">
+        <v>970</v>
+      </c>
+      <c r="J50" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="12"/>
+        <v>470</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>

--- a/12609979.2.xlsx
+++ b/12609979.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{5ACB5D22-18EE-4E8C-AA38-09B6EED47307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{691D1AA9-2311-49A0-B3D3-7AC8D634A2CE}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{5ACB5D22-18EE-4E8C-AA38-09B6EED47307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E67C0CB0-C6FD-4D8D-A0E0-528CE9C94E0C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t xml:space="preserve">stressful day </t>
+  </si>
+  <si>
+    <t xml:space="preserve">travelling to home </t>
   </si>
 </sst>
 </file>
@@ -3185,70 +3188,140 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="10" t="str">
+      <c r="A51" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B51" s="9">
+        <v>450</v>
+      </c>
+      <c r="C51" s="9">
+        <v>70</v>
+      </c>
+      <c r="D51" s="9">
+        <v>60</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0</v>
+      </c>
+      <c r="F51" s="9">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0</v>
+      </c>
+      <c r="H51" s="9">
+        <v>600</v>
+      </c>
+      <c r="I51" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="10" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J51" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
+        <v>260</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N51" s="12"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="10" t="str">
+      <c r="A52" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B52" s="9">
+        <v>450</v>
+      </c>
+      <c r="C52" s="9">
+        <v>70</v>
+      </c>
+      <c r="D52" s="9">
+        <v>60</v>
+      </c>
+      <c r="E52" s="9">
+        <v>20</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>420</v>
+      </c>
+      <c r="I52" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="10" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J52" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="12"/>
+        <v>420</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="12" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="10" t="str">
+      <c r="A53" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B53" s="9">
+        <v>450</v>
+      </c>
+      <c r="C53" s="9">
+        <v>120</v>
+      </c>
+      <c r="D53" s="9">
+        <v>0</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0</v>
+      </c>
+      <c r="F53" s="9">
+        <v>0</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0</v>
+      </c>
+      <c r="H53" s="9">
+        <v>480</v>
+      </c>
+      <c r="I53" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="10" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J53" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="12"/>
+        <v>390</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" s="12" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>

--- a/12609979.2.xlsx
+++ b/12609979.2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prakr\OneDrive\Desktop\git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{5ACB5D22-18EE-4E8C-AA38-09B6EED47307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E67C0CB0-C6FD-4D8D-A0E0-528CE9C94E0C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,9 +295,6 @@
     <t>studying for ca</t>
   </si>
   <si>
-    <t>September</t>
-  </si>
-  <si>
     <t xml:space="preserve">learning </t>
   </si>
   <si>
@@ -359,6 +356,9 @@
   </si>
   <si>
     <t xml:space="preserve">travelling to home </t>
+  </si>
+  <si>
+    <t>October</t>
   </si>
 </sst>
 </file>
@@ -1051,7 +1051,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="G3" s="15"/>
     </row>
@@ -2264,7 +2264,7 @@
         <v>51</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2310,7 +2310,7 @@
         <v>64</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2356,7 +2356,7 @@
         <v>51</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2402,7 +2402,7 @@
         <v>64</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2448,7 +2448,7 @@
         <v>51</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2494,7 +2494,7 @@
         <v>51</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2540,7 +2540,7 @@
         <v>64</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2586,7 +2586,7 @@
         <v>51</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2632,7 +2632,7 @@
         <v>51</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -2678,7 +2678,7 @@
         <v>51</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2724,7 +2724,7 @@
         <v>51</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2770,7 +2770,7 @@
         <v>51</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
@@ -2816,7 +2816,7 @@
         <v>64</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2862,7 +2862,7 @@
         <v>64</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2908,7 +2908,7 @@
         <v>51</v>
       </c>
       <c r="N44" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2954,7 +2954,7 @@
         <v>51</v>
       </c>
       <c r="N45" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -2997,10 +2997,10 @@
         <v>50</v>
       </c>
       <c r="M46" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="N46" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="N46" s="12" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3043,10 +3043,10 @@
         <v>50</v>
       </c>
       <c r="M47" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N47" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3092,7 +3092,7 @@
         <v>64</v>
       </c>
       <c r="N48" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
@@ -3184,7 +3184,7 @@
         <v>64</v>
       </c>
       <c r="N50" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -3274,7 +3274,7 @@
         <v>51</v>
       </c>
       <c r="N52" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -3320,29 +3320,51 @@
         <v>51</v>
       </c>
       <c r="N53" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="8"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="10" t="str">
+      <c r="A54" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B54" s="9">
+        <v>450</v>
+      </c>
+      <c r="C54" s="9">
+        <v>60</v>
+      </c>
+      <c r="D54" s="9">
+        <v>120</v>
+      </c>
+      <c r="E54" s="9">
+        <v>60</v>
+      </c>
+      <c r="F54" s="9">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>480</v>
+      </c>
+      <c r="I54" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="10" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J54" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
+        <v>270</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N54" s="12"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.2.xlsx
+++ b/12609979.2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prakr\OneDrive\Desktop\git\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F186C7B-6B3D-4A43-B4CF-AAEE6BA225A1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>October</t>
+  </si>
+  <si>
+    <t>not able to focus much on studies</t>
   </si>
 </sst>
 </file>
@@ -3323,7 +3326,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>46296</v>
       </c>
@@ -3365,7 +3368,9 @@
       <c r="M54" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N54" s="12"/>
+      <c r="N54" s="12" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>

--- a/12609979.2.xlsx
+++ b/12609979.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F186C7B-6B3D-4A43-B4CF-AAEE6BA225A1}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A2D32AA-D611-4ED4-B058-21A7925CF2D4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3373,26 +3373,50 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="8"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="10" t="str">
+      <c r="A55" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B55" s="9">
+        <v>450</v>
+      </c>
+      <c r="C55" s="9">
+        <v>60</v>
+      </c>
+      <c r="D55" s="9">
+        <v>120</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0</v>
+      </c>
+      <c r="F55" s="9">
+        <v>0</v>
+      </c>
+      <c r="G55" s="9">
+        <v>0</v>
+      </c>
+      <c r="H55" s="9">
+        <v>360</v>
+      </c>
+      <c r="I55" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="10" t="str">
+        <v>990</v>
+      </c>
+      <c r="J55" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="12"/>
+        <v>450</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>

--- a/12609979.2.xlsx
+++ b/12609979.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A2D32AA-D611-4ED4-B058-21A7925CF2D4}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67D00821-EC0D-4A89-9873-392116FBD718}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3418,27 +3418,51 @@
         <v>94</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="8"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="10" t="str">
+    <row r="56" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="8">
+        <v>46298</v>
+      </c>
+      <c r="B56" s="9">
+        <v>450</v>
+      </c>
+      <c r="C56" s="9">
+        <v>60</v>
+      </c>
+      <c r="D56" s="9">
+        <v>120</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0</v>
+      </c>
+      <c r="F56" s="9">
+        <v>0</v>
+      </c>
+      <c r="G56" s="9">
+        <v>0</v>
+      </c>
+      <c r="H56" s="9">
+        <v>480</v>
+      </c>
+      <c r="I56" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="10" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J56" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="12"/>
+        <v>330</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N56" s="12" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="8"/>

--- a/12609979.2.xlsx
+++ b/12609979.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67D00821-EC0D-4A89-9873-392116FBD718}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E876121-80FB-47E1-B655-2D6DA539020F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>not able to focus much on studies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">studying for exam </t>
   </si>
 </sst>
 </file>
@@ -3465,26 +3468,50 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="8"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="10" t="str">
+      <c r="A57" s="8">
+        <v>46299</v>
+      </c>
+      <c r="B57" s="9">
+        <v>450</v>
+      </c>
+      <c r="C57" s="9">
+        <v>60</v>
+      </c>
+      <c r="D57" s="9">
+        <v>120</v>
+      </c>
+      <c r="E57" s="9">
+        <v>0</v>
+      </c>
+      <c r="F57" s="9">
+        <v>0</v>
+      </c>
+      <c r="G57" s="9">
+        <v>0</v>
+      </c>
+      <c r="H57" s="9">
+        <v>600</v>
+      </c>
+      <c r="I57" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="10" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J57" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="12"/>
+        <v>210</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="12" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="8"/>

--- a/12609979.2.xlsx
+++ b/12609979.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E876121-80FB-47E1-B655-2D6DA539020F}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C665987-1482-40FC-A455-540AB253CCC1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3514,25 +3514,47 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="10" t="str">
+      <c r="A58" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B58" s="9">
+        <v>430</v>
+      </c>
+      <c r="C58" s="9">
+        <v>60</v>
+      </c>
+      <c r="D58" s="9">
+        <v>180</v>
+      </c>
+      <c r="E58" s="9">
+        <v>20</v>
+      </c>
+      <c r="F58" s="9">
+        <v>200</v>
+      </c>
+      <c r="G58" s="9">
+        <v>4</v>
+      </c>
+      <c r="H58" s="9">
+        <v>360</v>
+      </c>
+      <c r="I58" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="10" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J58" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
+        <v>190</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N58" s="12"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">

--- a/12609979.2.xlsx
+++ b/12609979.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C665987-1482-40FC-A455-540AB253CCC1}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AD8A27F-7A33-4C2F-B83C-F97942153D30}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t xml:space="preserve">studying for exam </t>
+  </si>
+  <si>
+    <t>studied c++  for mid term</t>
   </si>
 </sst>
 </file>
@@ -3558,26 +3561,50 @@
       <c r="N58" s="12"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="10" t="str">
+      <c r="A59" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B59" s="9">
+        <v>430</v>
+      </c>
+      <c r="C59" s="9">
+        <v>60</v>
+      </c>
+      <c r="D59" s="9">
+        <v>120</v>
+      </c>
+      <c r="E59" s="9">
+        <v>30</v>
+      </c>
+      <c r="F59" s="9">
+        <v>250</v>
+      </c>
+      <c r="G59" s="9">
+        <v>5</v>
+      </c>
+      <c r="H59" s="9">
+        <v>420</v>
+      </c>
+      <c r="I59" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="10" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J59" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="12"/>
+        <v>130</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N59" s="12" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>

--- a/12609979.2.xlsx
+++ b/12609979.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ae226d8917d40bd/Desktop/git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AD8A27F-7A33-4C2F-B83C-F97942153D30}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{2EF4CDF0-D654-4CB5-BAF9-8556C76D0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE4CABB7-DD8B-4CF2-9579-24AE2FF37B5C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3607,25 +3607,47 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="10" t="str">
+      <c r="A60" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B60" s="9">
+        <v>400</v>
+      </c>
+      <c r="C60" s="9">
+        <v>60</v>
+      </c>
+      <c r="D60" s="9">
+        <v>120</v>
+      </c>
+      <c r="E60" s="9">
+        <v>0</v>
+      </c>
+      <c r="F60" s="9">
+        <v>250</v>
+      </c>
+      <c r="G60" s="9">
+        <v>5</v>
+      </c>
+      <c r="H60" s="9">
+        <v>480</v>
+      </c>
+      <c r="I60" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="10" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J60" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="11"/>
+        <v>130</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N60" s="12"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
